--- a/education_surveys/019_digital_teaching_story_submission_registration_form--education_surveys.xlsx
+++ b/education_surveys/019_digital_teaching_story_submission_registration_form--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,114 +520,122 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>submission_story</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>Please share your teaching story</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>submission_title</t>
+          <t>submission_category</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>submission_title</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>submission_description</t>
+          <t>submission_title</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>submission_description</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Briefly describe your teaching story</t>
+          <t>Please enter a title</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>submission_tags</t>
+          <t>submission_description</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>submission_tags</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A brief description of your submission</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>submission_tags</t>
+          <t>submission_file</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>submission_tags</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Attachment</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please upload a file</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -639,12 +647,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>submission_image</t>
+          <t>submission_audio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>submission_image</t>
+          <t>Audio</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -662,12 +670,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>submission_audio</t>
+          <t>submission_video</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>submission_audio</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,18 +693,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>submission_video</t>
+          <t>submission_email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>submission_video</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -708,12 +716,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>submission_file</t>
+          <t>submission_phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>submission_file</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -726,17 +734,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>submission_file_2</t>
+          <t>submission_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>submission_file_2</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,17 +757,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>submission_email</t>
+          <t>submission_time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>submission_email</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -777,200 +785,16 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>submission_phone</t>
+          <t>submission_location</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>submission_phone</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>submission_date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>submission_time</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>submission_date_range</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>submission_date_range</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>submission_time_range</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>submission_time_range</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>submission_venue</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>submission_venue</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>submission_venue</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>submission_venue</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>submission_venue</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>submission_venue</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>submission_venue</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>submission_venue</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -987,12 +811,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1015,238 +839,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>submission_tags_choices</t>
+          <t>submission_category_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>academic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Academic</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>submission_tags_choices</t>
+          <t>submission_category_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>non-academic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Non-Academic</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>submission_tags_choices</t>
+          <t>submission_category_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>submission_tags_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>submission_tags_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>submission_tags_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>submission_venue_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>venue-1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>venue-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>submission_venue_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>venue-2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>venue-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>submission_venue_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>venue-1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>venue-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>submission_venue_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>venue-2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>venue-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>submission_venue_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>venue-1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>venue-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>submission_venue_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>venue-2</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>venue-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>submission_venue_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>venue-1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>venue-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>submission_venue_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>venue-2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>venue-2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
